--- a/survey_templates/009_child_development_excursion_policy_survey--survey_templates.xlsx
+++ b/survey_templates/009_child_development_excursion_policy_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -835,8 +835,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -864,12 +864,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_read_and_understood',_'value':_true}</t>
+          <t>yes_-_read_and_understood</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Read and Understood', 'value': True}</t>
+          <t>Yes - Read and Understood</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_need_a_copy',_'value':_false}</t>
+          <t>no_-_need_a_copy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'No - Need a Copy', 'value': False}</t>
+          <t>No - Need a Copy</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'walking_excursions_in_local_area',_'value':_'walking'}</t>
+          <t>walking_excursions_in_local_area</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Walking excursions in local area', 'value': 'walking'}</t>
+          <t>Walking excursions in local area</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'bus_excursions_to_regional_sites',_'value':_'bus'}</t>
+          <t>bus_excursions_to_regional_sites</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Bus excursions to regional sites', 'value': 'bus'}</t>
+          <t>Bus excursions to regional sites</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'visits_to_local_parks',_'value':_'park'}</t>
+          <t>visits_to_local_parks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Visits to local parks', 'value': 'park'}</t>
+          <t>Visits to local parks</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'library_and_community_visits',_'value':_'community'}</t>
+          <t>library_and_community_visits</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Library and community visits', 'value': 'community'}</t>
+          <t>Library and community visits</t>
         </is>
       </c>
     </row>
